--- a/quizzes/008_cotton_knowledge_quiz--quizzes.xlsx
+++ b/quizzes/008_cotton_knowledge_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>Welcome to the Cotton Knowledge Quiz</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,40 +538,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>quiz_questions</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>quiz_questions</t>
+          <t>What is cotton?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>What is the primary use of cotton in the textile industry?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>How many types of cotton fiber are there?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>What is the process of treating cotton to make it more durable?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>How many steps are involved in the cotton production process?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>What is the main difference between natural and synthetic fibers?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>What is the term for the natural fiber that is used to create cotton fabric?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>How does cotton get its unique texture and durability?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>How can cotton be treated to make it more resistant to wrinkles?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>last_page</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>last_page</t>
+          <t>What are some common uses of cotton in daily life?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>last_page</t>
+          <t>last_question</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>last_page</t>
+          <t>What is the final score of the quiz?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,34 +827,425 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quiz_questions_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'question_1',_'value':_'question_1_value'}</t>
+          <t>fiber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'question_1', 'value': 'question_1_value'}</t>
+          <t>fiber</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quiz_questions_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'question_2',_'value':_'question_2_value'}</t>
+          <t>fabric</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'question_2', 'value': 'question_2_value'}</t>
+          <t>fabric</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>question_2_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>yarn</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yarn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>question_3_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>long-staple</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>long-staple</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>question_3_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>short-staple</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>short-staple</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>question_3_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>extral-long</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>extral-long</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>bleaching</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bleaching</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>printing</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>printing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>question_4_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dyeing</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>dyeing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ginning</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ginning</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>carding</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>carding</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>weaving</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>weaving</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>question_5_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>spinning</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>spinning</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>breathability</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>breathability</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>elasticity</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>elasticity</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>question_6_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>water-resistance</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>water-resistance</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>thread</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>thread</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>yarn</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>yarn</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>thread-count</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>thread-count</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>starching</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>starching</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bleaching</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>bleaching</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ironing</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ironing</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>clothing</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>clothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>bedding</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>bedding</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>towels</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>towels</t>
         </is>
       </c>
     </row>
